--- a/standalone-assessment/source/AI_Opportunity_Assessment_v2_WIP_3.xlsx
+++ b/standalone-assessment/source/AI_Opportunity_Assessment_v2_WIP_3.xlsx
@@ -1042,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y51"/>
+  <dimension ref="A1:Y44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="22.140625" bestFit="1" customWidth="1" style="44" min="1" max="1"/>
@@ -3021,7 +3021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.140625" bestFit="1" customWidth="1" style="31" min="1" max="1"/>
@@ -3401,43 +3401,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30.75" customHeight="1" s="44">
-      <c r="A11" s="37" t="inlineStr">
-        <is>
-          <t>Annual OpEx Cost</t>
-        </is>
-      </c>
-      <c r="B11" s="32" t="inlineStr">
-        <is>
-          <t>What incremental annual OpEx does this add?</t>
-        </is>
-      </c>
-      <c r="C11" s="28" t="inlineStr">
-        <is>
-          <t>Negligible. Absorbed in existing run costs</t>
-        </is>
-      </c>
-      <c r="D11" s="28" t="inlineStr">
-        <is>
-          <t>&lt;$20K annually</t>
-        </is>
-      </c>
-      <c r="E11" s="28" t="inlineStr">
-        <is>
-          <t>$20-50K annually</t>
-        </is>
-      </c>
-      <c r="F11" s="28" t="inlineStr">
-        <is>
-          <t>$50-300k annually</t>
-        </is>
-      </c>
-      <c r="G11" s="28" t="inlineStr">
-        <is>
-          <t>&gt;300k Annually</t>
-        </is>
-      </c>
-    </row>
+    <row r="11" ht="30.75" customHeight="1" s="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
@@ -3450,7 +3414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col width="55.7109375" bestFit="1" customWidth="1" style="15" min="1" max="1"/>
@@ -3568,48 +3532,38 @@
         </is>
       </c>
       <c r="B12" s="19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="44">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>Annual OpEx Cost</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="A13" s="17" t="n"/>
+      <c r="B13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="n"/>
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>AI Opportunity Score</t>
+        </is>
+      </c>
       <c r="B14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>AI Opportunity Score</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="n"/>
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Impact Score</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>Impact Score</t>
+          <t>Feasibility Score</t>
         </is>
       </c>
       <c r="B16" s="19" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>Feasibility Score</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="n">
         <v>0.4</v>
       </c>
     </row>

--- a/standalone-assessment/source/AI_Opportunity_Assessment_v2_WIP_3.xlsx
+++ b/standalone-assessment/source/AI_Opportunity_Assessment_v2_WIP_3.xlsx
@@ -1110,7 +1110,7 @@
       </c>
       <c r="E2" s="49" t="inlineStr">
         <is>
-          <t>Financial Impact 
+          <t>Net Financial Impact 
 (Revenue or Margin Growth, Losses Prevented)</t>
         </is>
       </c>
@@ -3065,7 +3065,7 @@
     <row r="2" ht="45.75" customHeight="1" s="44">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>Financial Impact 
+          <t>Net Financial Impact 
 (revenue/margin growth, loss prevention)</t>
         </is>
       </c>
@@ -3433,7 +3433,7 @@
     <row r="2" ht="15" customHeight="1" s="44">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>Financial Impact 
+          <t>Net Financial Impact 
 (revenue/margin growth, loss prevention)</t>
         </is>
       </c>

--- a/standalone-assessment/source/AI_Opportunity_Assessment_v2_WIP_3.xlsx
+++ b/standalone-assessment/source/AI_Opportunity_Assessment_v2_WIP_3.xlsx
@@ -3076,7 +3076,7 @@
       </c>
       <c r="C2" s="28" t="inlineStr">
         <is>
-          <t>Not measurable</t>
+          <t>Not measurable or no impact</t>
         </is>
       </c>
       <c r="D2" s="28" t="inlineStr">
@@ -3086,17 +3086,17 @@
       </c>
       <c r="E2" s="28" t="inlineStr">
         <is>
-          <t>$100–500K annually</t>
+          <t>$100–300K annually</t>
         </is>
       </c>
       <c r="F2" s="28" t="inlineStr">
         <is>
-          <t>$500K–$2M annually</t>
+          <t>$300K–1M annually</t>
         </is>
       </c>
       <c r="G2" s="28" t="inlineStr">
         <is>
-          <t>&gt; $2M annually</t>
+          <t>&gt; $1M annually</t>
         </is>
       </c>
     </row>
@@ -3377,22 +3377,22 @@
       </c>
       <c r="C10" s="28" t="inlineStr">
         <is>
-          <t>None, Absorbed in existing licenses</t>
+          <t>No additional CapEx</t>
         </is>
       </c>
       <c r="D10" s="28" t="inlineStr">
         <is>
-          <t>&lt;$100k</t>
+          <t>&lt;$50K</t>
         </is>
       </c>
       <c r="E10" s="28" t="inlineStr">
         <is>
-          <t>$100–300K</t>
+          <t>$50K–150K</t>
         </is>
       </c>
       <c r="F10" s="28" t="inlineStr">
         <is>
-          <t>$300K–$500K</t>
+          <t>$150K–$500K</t>
         </is>
       </c>
       <c r="G10" s="28" t="inlineStr">

--- a/standalone-assessment/source/AI_Opportunity_Assessment_v2_WIP_3.xlsx
+++ b/standalone-assessment/source/AI_Opportunity_Assessment_v2_WIP_3.xlsx
@@ -3081,22 +3081,22 @@
       </c>
       <c r="D2" s="28" t="inlineStr">
         <is>
-          <t>&lt;$100K annually</t>
+          <t>&lt;$50K annually</t>
         </is>
       </c>
       <c r="E2" s="28" t="inlineStr">
         <is>
-          <t>$100–300K annually</t>
+          <t>$50–200K annually</t>
         </is>
       </c>
       <c r="F2" s="28" t="inlineStr">
         <is>
-          <t>$300K–1M annually</t>
+          <t>$200K–700K annually</t>
         </is>
       </c>
       <c r="G2" s="28" t="inlineStr">
         <is>
-          <t>&gt; $1M annually</t>
+          <t>&gt; $700K annually</t>
         </is>
       </c>
     </row>
@@ -3387,17 +3387,17 @@
       </c>
       <c r="E10" s="28" t="inlineStr">
         <is>
-          <t>$50K–150K</t>
+          <t>$50K–200K</t>
         </is>
       </c>
       <c r="F10" s="28" t="inlineStr">
         <is>
-          <t>$150K–$500K</t>
+          <t>$200K–$700K</t>
         </is>
       </c>
       <c r="G10" s="28" t="inlineStr">
         <is>
-          <t>&gt; $500K</t>
+          <t>&gt; $700K</t>
         </is>
       </c>
     </row>
